--- a/CPL I CARD MAKER.xlsx
+++ b/CPL I CARD MAKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lalne\OneDrive\Desktop\icard-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863201A2-2F66-4716-AE29-7C1986B03DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA9D77-F9BB-4165-BB9D-76132E548EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="779" xr2:uid="{35249704-93DD-46CD-A91B-7B3A76021797}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="610">
   <si>
     <t>MAZ</t>
   </si>
@@ -2464,6 +2464,91 @@
   </si>
   <si>
     <t>9601 9192 7858</t>
+  </si>
+  <si>
+    <t>S/NO</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>TRADE</t>
+  </si>
+  <si>
+    <t>NAME 
+(IN CAPITAL LETTERS)</t>
+  </si>
+  <si>
+    <t>DATE OF
+ BIRTH</t>
+  </si>
+  <si>
+    <t>FATHER'S NAME
+(IN CAPITAL LETTERS)</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoK Details
+ (Name and Address) </t>
+  </si>
+  <si>
+    <t>Adhar No./Any valid Govt docs</t>
+  </si>
+  <si>
+    <t>Insurance 
+scheme</t>
+  </si>
+  <si>
+    <t>Pension
+scheme</t>
+  </si>
+  <si>
+    <t>WORKER 
+ID CARD
+STATUS</t>
+  </si>
+  <si>
+    <t>E-SHRAM 
+STATUS</t>
+  </si>
+  <si>
+    <t>AYUSHMAN CARD</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t>BANK A/C NO</t>
+  </si>
+  <si>
+    <t>IFS CODE</t>
+  </si>
+  <si>
+    <t>WORKING
+DAYS</t>
+  </si>
+  <si>
+    <t>P/DAY
+RATES</t>
+  </si>
+  <si>
+    <t>NET 
+AMT</t>
+  </si>
+  <si>
+    <t>PAGE AMT 
+TOTAL</t>
+  </si>
+  <si>
+    <t>MANDATE FORM STATUS</t>
+  </si>
+  <si>
+    <t>Date of Enrolment</t>
+  </si>
+  <si>
+    <t>Date of Discharge</t>
   </si>
 </sst>
 </file>
@@ -2476,7 +2561,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2542,8 +2627,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2553,6 +2644,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2636,7 +2733,7 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2795,6 +2892,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2807,9 +2928,29 @@
   </cellStyles>
   <dxfs count="46">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3237,23 +3378,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3592,7 +3716,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A2:X112"/>
+  <dimension ref="A1:X112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
@@ -3608,9 +3732,83 @@
     <col min="16" max="16" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="72.6640625" customWidth="1"/>
+    <col min="23" max="23" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:24" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>588</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>589</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>590</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>591</v>
+      </c>
+      <c r="G1" s="57" t="s">
+        <v>592</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>593</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>594</v>
+      </c>
+      <c r="J1" s="55" t="s">
+        <v>595</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>596</v>
+      </c>
+      <c r="L1" s="55" t="s">
+        <v>597</v>
+      </c>
+      <c r="M1" s="55" t="s">
+        <v>598</v>
+      </c>
+      <c r="N1" s="58" t="s">
+        <v>599</v>
+      </c>
+      <c r="O1" s="59" t="s">
+        <v>600</v>
+      </c>
+      <c r="P1" s="54" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q1" s="56" t="s">
+        <v>602</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>603</v>
+      </c>
+      <c r="S1" s="55" t="s">
+        <v>604</v>
+      </c>
+      <c r="T1" s="60" t="s">
+        <v>605</v>
+      </c>
+      <c r="U1" s="55" t="s">
+        <v>606</v>
+      </c>
+      <c r="V1" s="61" t="s">
+        <v>607</v>
+      </c>
+      <c r="W1" s="56" t="s">
+        <v>608</v>
+      </c>
+      <c r="X1" s="55" t="s">
+        <v>609</v>
+      </c>
+    </row>
     <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
@@ -10695,150 +10893,148 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:N69">
-    <cfRule type="containsBlanks" dxfId="45" priority="44">
+    <cfRule type="containsBlanks" dxfId="45" priority="45">
       <formula>LEN(TRIM(J2))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M70:O112">
+    <cfRule type="containsBlanks" dxfId="44" priority="2">
+      <formula>LEN(TRIM(M70))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P69">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:T69">
-    <cfRule type="containsBlanks" dxfId="43" priority="45">
+  <conditionalFormatting sqref="P70">
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P71">
+    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P72">
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P73">
+    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P74">
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P75">
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P76">
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P77">
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P78">
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P79">
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P80">
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P81">
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P82">
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P83">
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P84">
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P85">
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P86">
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P87">
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P88">
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P89">
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P90">
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P91">
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P92">
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P93">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P94">
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P95">
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P96">
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P97">
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P98">
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P99">
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P100">
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P101">
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P102">
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P103">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P104">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P105">
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P106">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P107">
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P108">
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P109">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P110:P112">
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:T112">
+    <cfRule type="containsBlanks" dxfId="1" priority="3">
       <formula>LEN(TRIM(S2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M70:O112">
-    <cfRule type="containsBlanks" dxfId="42" priority="1">
-      <formula>LEN(TRIM(M70))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P70">
-    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P71">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P72">
-    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P73">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P74">
-    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P75">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P76">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P77">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P78">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P79">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P80">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P81">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P82">
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P83">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P84">
-    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P85">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P86">
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P87">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P88">
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P89">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P90">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P91">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P92">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P93">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P94">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P95">
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P96">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P97">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P98">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P99">
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P100">
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P101">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P102">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P103">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P104">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P105">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P106">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P107">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P108">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P109">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P110:P112">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S70:T112">
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(S70))=0</formula>
-    </cfRule>
+  <conditionalFormatting sqref="P1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
